--- a/results_combat/solution_SUBMIT.xlsx
+++ b/results_combat/solution_SUBMIT.xlsx
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -628,10 +628,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>37.0406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -647,7 +647,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -715,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.1479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5.4097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.0055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.6438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.8773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>8.856999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.4252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.9499</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.1847</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1443,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.7273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.0075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>3.5622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.8348</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2.3038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1695,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>5.0742</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>3.5598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>19.2463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>6.0276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1947,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>2.0102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>5.0476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>7.1739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2.1286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>5.7696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>26.4883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2227,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>8.176299999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2255,7 +2255,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>2.3113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>3.9155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>10.9552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>11.4637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>3.9384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>9.0052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>15.6824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>12.6017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -3095,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>9.246499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>4.3062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>4.7227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>8.011699999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>4.3313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>8.783099999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3515,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>6.4123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>5.6376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>2.562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3767,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>16.4159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>5.6507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3851,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>2.3122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>10.6545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>1.8485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>2.0091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3991,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>2.1176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>1.8236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>3.0231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>7.6652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>5.1601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -4159,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>2.3768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>3.0906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4243,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>2.1483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -4371,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>27.8082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>3.7266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>5.6688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -4579,7 +4579,7 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>2.4884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -4691,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>3.9639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>3.5471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -4816,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -4912,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -4928,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>5.5847</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>1.918</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>4.9632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -5503,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>5.2415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>3.5472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>1.9006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -5584,7 +5584,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5712,7 +5712,7 @@
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
@@ -5752,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5780,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5836,7 +5836,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>2.8498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D200" t="n">
         <v>0</v>
@@ -6029,10 +6029,10 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>1231</v>
       </c>
       <c r="G200" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -6060,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6079,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -6088,10 +6088,10 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>16.7115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -6119,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>2.7769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -6147,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>6.3435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -6203,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>13.4864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -6315,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>2.5884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -6371,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>3.7209</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>5.1338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -6427,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>4.7802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -6455,7 +6455,7 @@
         <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>6.5994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -6483,7 +6483,7 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>2.1262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -6499,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>25.6254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -6539,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>17.3572</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -6564,10 +6564,10 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>10.9433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -6595,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>3.2006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -6763,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -6931,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>2.9403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -6959,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>1.9538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -7211,7 +7211,7 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>3.5392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -7376,10 +7376,10 @@
         <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>37.8965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="C249" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D249" t="n">
         <v>0</v>
@@ -7404,10 +7404,10 @@
         <v>0</v>
       </c>
       <c r="G249" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>18.5606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -7603,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>1.8454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -7631,7 +7631,7 @@
         <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>5.3165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -7644,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D258" t="n">
         <v>0</v>
@@ -7656,10 +7656,10 @@
         <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>34.3075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -7672,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -7684,10 +7684,10 @@
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>34.4915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -7883,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="H266" t="n">
-        <v>2.0701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -7911,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="H267" t="n">
-        <v>1.9578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -7939,7 +7939,7 @@
         <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>10.8913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -7967,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="H269" t="n">
-        <v>11.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -8023,7 +8023,7 @@
         <v>0</v>
       </c>
       <c r="H271" t="n">
-        <v>2.2983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -8079,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>2.4164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -8107,7 +8107,7 @@
         <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>1.8278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -8191,7 +8191,7 @@
         <v>0</v>
       </c>
       <c r="H277" t="n">
-        <v>5.373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -8260,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="C280" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D280" t="n">
         <v>0</v>
@@ -8272,7 +8272,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D281" t="n">
         <v>0</v>
@@ -8297,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="C282" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D282" t="n">
         <v>0</v>
@@ -8328,7 +8328,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H282" t="n">
         <v>55.0897</v>
@@ -8387,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="H284" t="n">
-        <v>2.3002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>1.8462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -8555,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="H290" t="n">
-        <v>4.8435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -8583,7 +8583,7 @@
         <v>0</v>
       </c>
       <c r="H291" t="n">
-        <v>2.9195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -8611,7 +8611,7 @@
         <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>2.4095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -8627,7 +8627,7 @@
         <v>0</v>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E293" t="n">
         <v>0</v>
@@ -8667,7 +8667,7 @@
         <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>7.2197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -8680,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D295" t="n">
         <v>0</v>
@@ -8689,7 +8689,7 @@
         <v>0</v>
       </c>
       <c r="F295" t="n">
-        <v>2303</v>
+        <v>0</v>
       </c>
       <c r="G295" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>0</v>
       </c>
       <c r="H298" t="n">
-        <v>11.0649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -8792,7 +8792,7 @@
         <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D299" t="n">
         <v>0</v>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D300" t="n">
         <v>0</v>
@@ -8832,7 +8832,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -8848,7 +8848,7 @@
         <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D301" t="n">
         <v>0</v>
@@ -8891,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>5.5017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -8919,7 +8919,7 @@
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>5.5362</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -8947,7 +8947,7 @@
         <v>0</v>
       </c>
       <c r="H304" t="n">
-        <v>5.2559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -9000,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9044,7 +9044,7 @@
         <v>0</v>
       </c>
       <c r="C308" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D308" t="n">
         <v>0</v>
@@ -9087,7 +9087,7 @@
         <v>0</v>
       </c>
       <c r="H309" t="n">
-        <v>9.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -9103,7 +9103,7 @@
         <v>0</v>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E310" t="n">
         <v>0</v>
@@ -9112,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
         <v>0</v>
       </c>
       <c r="H311" t="n">
-        <v>10.4983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -9199,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>6.645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="H315" t="n">
-        <v>19.682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -9283,7 +9283,7 @@
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>2.8933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -9311,7 +9311,7 @@
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>5.0651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -9367,7 +9367,7 @@
         <v>0</v>
       </c>
       <c r="H319" t="n">
-        <v>2.7774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -9395,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>1.7801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -9408,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="C321" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D321" t="n">
         <v>0</v>
@@ -9420,10 +9420,10 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H321" t="n">
-        <v>40.0723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -9451,7 +9451,7 @@
         <v>0</v>
       </c>
       <c r="H322" t="n">
-        <v>3.1781</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -9479,7 +9479,7 @@
         <v>0</v>
       </c>
       <c r="H323" t="n">
-        <v>2.7183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -9535,7 +9535,7 @@
         <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>2.0237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -9619,7 +9619,7 @@
         <v>0</v>
       </c>
       <c r="H328" t="n">
-        <v>2.0038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -9647,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>4.6766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -9675,7 +9675,7 @@
         <v>0</v>
       </c>
       <c r="H330" t="n">
-        <v>3.0729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -9703,7 +9703,7 @@
         <v>0</v>
       </c>
       <c r="H331" t="n">
-        <v>2.5609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -9815,7 +9815,7 @@
         <v>0</v>
       </c>
       <c r="H335" t="n">
-        <v>1.9034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -9927,7 +9927,7 @@
         <v>0</v>
       </c>
       <c r="H339" t="n">
-        <v>1.884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -9955,7 +9955,7 @@
         <v>0</v>
       </c>
       <c r="H340" t="n">
-        <v>1.8994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -9983,7 +9983,7 @@
         <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>3.1459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -10095,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>6.7186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -10123,7 +10123,7 @@
         <v>0</v>
       </c>
       <c r="H346" t="n">
-        <v>3.3696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -10179,7 +10179,7 @@
         <v>0</v>
       </c>
       <c r="H348" t="n">
-        <v>2.9688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -10263,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>2.0164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
@@ -10319,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="H353" t="n">
-        <v>2.6625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -10347,7 +10347,7 @@
         <v>0</v>
       </c>
       <c r="H354" t="n">
-        <v>2.7401</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -10403,7 +10403,7 @@
         <v>0</v>
       </c>
       <c r="H356" t="n">
-        <v>3.8302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -10487,7 +10487,7 @@
         <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>3.1152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -10500,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="C360" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D360" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>36.4345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -10559,7 +10559,7 @@
         <v>0</v>
       </c>
       <c r="D362" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E362" t="n">
         <v>0</v>
@@ -10599,7 +10599,7 @@
         <v>0</v>
       </c>
       <c r="H363" t="n">
-        <v>4.0775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -10615,7 +10615,7 @@
         <v>0</v>
       </c>
       <c r="D364" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E364" t="n">
         <v>0</v>
@@ -10624,10 +10624,10 @@
         <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H364" t="n">
-        <v>25.0048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -10655,7 +10655,7 @@
         <v>0</v>
       </c>
       <c r="H365" t="n">
-        <v>8.417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -10683,7 +10683,7 @@
         <v>0</v>
       </c>
       <c r="H366" t="n">
-        <v>2.0749</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -10711,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="H367" t="n">
-        <v>6.3151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -10767,7 +10767,7 @@
         <v>0</v>
       </c>
       <c r="H369" t="n">
-        <v>3.7807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -10783,7 +10783,7 @@
         <v>0</v>
       </c>
       <c r="D370" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E370" t="n">
         <v>0</v>
@@ -10795,7 +10795,7 @@
         <v>0</v>
       </c>
       <c r="H370" t="n">
-        <v>18.7288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -10851,7 +10851,7 @@
         <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>9.0791</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -10879,7 +10879,7 @@
         <v>0</v>
       </c>
       <c r="H373" t="n">
-        <v>8.7804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -11047,7 +11047,7 @@
         <v>0</v>
       </c>
       <c r="H379" t="n">
-        <v>2.9053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -11075,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="H380" t="n">
-        <v>7.8033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -11088,7 +11088,7 @@
         <v>0</v>
       </c>
       <c r="C381" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D381" t="n">
         <v>0</v>
@@ -11100,10 +11100,10 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H381" t="n">
-        <v>35.854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="C382" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D382" t="n">
         <v>0</v>
@@ -11128,10 +11128,10 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H382" t="n">
-        <v>48.2245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -11187,7 +11187,7 @@
         <v>0</v>
       </c>
       <c r="H384" t="n">
-        <v>5.7171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -11243,7 +11243,7 @@
         <v>0</v>
       </c>
       <c r="H386" t="n">
-        <v>15.5778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -11271,7 +11271,7 @@
         <v>0</v>
       </c>
       <c r="H387" t="n">
-        <v>2.1355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -11299,7 +11299,7 @@
         <v>0</v>
       </c>
       <c r="H388" t="n">
-        <v>1.9575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -11327,7 +11327,7 @@
         <v>0</v>
       </c>
       <c r="H389" t="n">
-        <v>2.3727</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -11355,7 +11355,7 @@
         <v>0</v>
       </c>
       <c r="H390" t="n">
-        <v>2.1948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -11383,7 +11383,7 @@
         <v>0</v>
       </c>
       <c r="H391" t="n">
-        <v>2.3829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -11411,7 +11411,7 @@
         <v>0</v>
       </c>
       <c r="H392" t="n">
-        <v>2.5604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393">
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="H394" t="n">
-        <v>2.8406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="H396" t="n">
-        <v>1.8323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -11551,7 +11551,7 @@
         <v>0</v>
       </c>
       <c r="H397" t="n">
-        <v>4.0086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -11579,7 +11579,7 @@
         <v>0</v>
       </c>
       <c r="H398" t="n">
-        <v>1.8464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399">
@@ -11607,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="H399" t="n">
-        <v>2.3404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -11635,7 +11635,7 @@
         <v>0</v>
       </c>
       <c r="H400" t="n">
-        <v>1.8315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="D401" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E401" t="n">
         <v>0</v>
@@ -11660,10 +11660,10 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H401" t="n">
-        <v>15.8874</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -11691,7 +11691,7 @@
         <v>0</v>
       </c>
       <c r="H402" t="n">
-        <v>3.2432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -11775,7 +11775,7 @@
         <v>0</v>
       </c>
       <c r="H405" t="n">
-        <v>2.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -11803,7 +11803,7 @@
         <v>0</v>
       </c>
       <c r="H406" t="n">
-        <v>4.0747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -11819,7 +11819,7 @@
         <v>0</v>
       </c>
       <c r="D407" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E407" t="n">
         <v>0</v>
@@ -11828,10 +11828,10 @@
         <v>0</v>
       </c>
       <c r="G407" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H407" t="n">
-        <v>26.3257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -11887,7 +11887,7 @@
         <v>0</v>
       </c>
       <c r="H409" t="n">
-        <v>4.0146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410">
@@ -11940,10 +11940,10 @@
         <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H411" t="n">
-        <v>7.5798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="H412" t="n">
-        <v>3.4853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413">
@@ -11999,7 +11999,7 @@
         <v>0</v>
       </c>
       <c r="H413" t="n">
-        <v>9.097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -12083,7 +12083,7 @@
         <v>0</v>
       </c>
       <c r="H416" t="n">
-        <v>3.7778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -12363,7 +12363,7 @@
         <v>0</v>
       </c>
       <c r="H426" t="n">
-        <v>8.323600000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427">
@@ -12391,7 +12391,7 @@
         <v>0</v>
       </c>
       <c r="H427" t="n">
-        <v>4.3785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -12435,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="D429" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E429" t="n">
         <v>0</v>
@@ -12587,7 +12587,7 @@
         <v>0</v>
       </c>
       <c r="H434" t="n">
-        <v>1.8316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435">
@@ -12615,7 +12615,7 @@
         <v>0</v>
       </c>
       <c r="H435" t="n">
-        <v>12.0388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436">
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="H436" t="n">
-        <v>3.3895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -12671,7 +12671,7 @@
         <v>0</v>
       </c>
       <c r="H437" t="n">
-        <v>3.3332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -12699,7 +12699,7 @@
         <v>0</v>
       </c>
       <c r="H438" t="n">
-        <v>2.7385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439">
@@ -12727,7 +12727,7 @@
         <v>0</v>
       </c>
       <c r="H439" t="n">
-        <v>3.2683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
@@ -12755,7 +12755,7 @@
         <v>0</v>
       </c>
       <c r="H440" t="n">
-        <v>5.0944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -12799,7 +12799,7 @@
         <v>0</v>
       </c>
       <c r="D442" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E442" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>0</v>
       </c>
       <c r="H443" t="n">
-        <v>7.4387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444">
@@ -12895,7 +12895,7 @@
         <v>0</v>
       </c>
       <c r="H445" t="n">
-        <v>3.6166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446">
@@ -12979,7 +12979,7 @@
         <v>0</v>
       </c>
       <c r="H448" t="n">
-        <v>4.6054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="449">
@@ -13063,7 +13063,7 @@
         <v>0</v>
       </c>
       <c r="H451" t="n">
-        <v>2.4753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -13091,7 +13091,7 @@
         <v>0</v>
       </c>
       <c r="H452" t="n">
-        <v>5.5336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -13147,7 +13147,7 @@
         <v>0</v>
       </c>
       <c r="H454" t="n">
-        <v>7.3725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -13175,7 +13175,7 @@
         <v>0</v>
       </c>
       <c r="H455" t="n">
-        <v>2.4206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456">
@@ -13287,7 +13287,7 @@
         <v>0</v>
       </c>
       <c r="H459" t="n">
-        <v>2.2423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="460">
@@ -13371,7 +13371,7 @@
         <v>0</v>
       </c>
       <c r="H462" t="n">
-        <v>4.8231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463">
@@ -13415,7 +13415,7 @@
         <v>0</v>
       </c>
       <c r="D464" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E464" t="n">
         <v>0</v>
@@ -13424,10 +13424,10 @@
         <v>0</v>
       </c>
       <c r="G464" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H464" t="n">
-        <v>20.8429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="465">
@@ -13511,7 +13511,7 @@
         <v>0</v>
       </c>
       <c r="H467" t="n">
-        <v>3.1421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="468">
@@ -13567,7 +13567,7 @@
         <v>0</v>
       </c>
       <c r="H469" t="n">
-        <v>38.2376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="470">
@@ -13595,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="H470" t="n">
-        <v>2.9023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -13623,7 +13623,7 @@
         <v>0</v>
       </c>
       <c r="H471" t="n">
-        <v>3.0136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472">
@@ -13651,7 +13651,7 @@
         <v>0</v>
       </c>
       <c r="H472" t="n">
-        <v>14.617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473">
@@ -13679,7 +13679,7 @@
         <v>0</v>
       </c>
       <c r="H473" t="n">
-        <v>2.6683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474">
@@ -13695,7 +13695,7 @@
         <v>0</v>
       </c>
       <c r="D474" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E474" t="n">
         <v>0</v>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="H474" t="n">
-        <v>32.4505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475">
@@ -13723,7 +13723,7 @@
         <v>0</v>
       </c>
       <c r="D475" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E475" t="n">
         <v>0</v>
@@ -13732,7 +13732,7 @@
         <v>0</v>
       </c>
       <c r="G475" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="H479" t="n">
-        <v>6.2361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -14071,7 +14071,7 @@
         <v>0</v>
       </c>
       <c r="H487" t="n">
-        <v>1.9448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488">
@@ -14127,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="H489" t="n">
-        <v>1.9544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="490">
@@ -14155,7 +14155,7 @@
         <v>0</v>
       </c>
       <c r="H490" t="n">
-        <v>3.6007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="491">
@@ -14183,7 +14183,7 @@
         <v>0</v>
       </c>
       <c r="H491" t="n">
-        <v>6.2706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="492">
@@ -14211,7 +14211,7 @@
         <v>0</v>
       </c>
       <c r="H492" t="n">
-        <v>3.0006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493">
@@ -14239,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="H493" t="n">
-        <v>7.133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494">
@@ -14267,7 +14267,7 @@
         <v>0</v>
       </c>
       <c r="H494" t="n">
-        <v>3.1381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="495">
@@ -14323,7 +14323,7 @@
         <v>0</v>
       </c>
       <c r="H496" t="n">
-        <v>3.787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497">
@@ -14351,7 +14351,7 @@
         <v>0</v>
       </c>
       <c r="H497" t="n">
-        <v>1.9522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498">
@@ -14407,7 +14407,7 @@
         <v>0</v>
       </c>
       <c r="H499" t="n">
-        <v>2.7823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -14491,7 +14491,7 @@
         <v>0</v>
       </c>
       <c r="H502" t="n">
-        <v>3.6465</v>
+        <v>0</v>
       </c>
     </row>
     <row r="503">
@@ -14855,7 +14855,7 @@
         <v>0</v>
       </c>
       <c r="H515" t="n">
-        <v>1.7423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516">
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="H522" t="n">
-        <v>3.1881</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523">
@@ -15079,7 +15079,7 @@
         <v>0</v>
       </c>
       <c r="H523" t="n">
-        <v>2.8929</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
@@ -15107,7 +15107,7 @@
         <v>0</v>
       </c>
       <c r="H524" t="n">
-        <v>2.5383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="525">
@@ -15135,7 +15135,7 @@
         <v>0</v>
       </c>
       <c r="H525" t="n">
-        <v>3.1938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="526">
@@ -15163,7 +15163,7 @@
         <v>0</v>
       </c>
       <c r="H526" t="n">
-        <v>4.7163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="527">
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="H527" t="n">
-        <v>9.250500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="528">
@@ -15219,7 +15219,7 @@
         <v>0</v>
       </c>
       <c r="H528" t="n">
-        <v>2.2522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="529">
@@ -15247,7 +15247,7 @@
         <v>0</v>
       </c>
       <c r="H529" t="n">
-        <v>2.9417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530">
@@ -15275,7 +15275,7 @@
         <v>0</v>
       </c>
       <c r="H530" t="n">
-        <v>4.1316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -15303,7 +15303,7 @@
         <v>0</v>
       </c>
       <c r="H531" t="n">
-        <v>2.2989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532">
@@ -15331,7 +15331,7 @@
         <v>0</v>
       </c>
       <c r="H532" t="n">
-        <v>3.183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533">
@@ -15359,7 +15359,7 @@
         <v>0</v>
       </c>
       <c r="H533" t="n">
-        <v>5.527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534">
@@ -15387,7 +15387,7 @@
         <v>0</v>
       </c>
       <c r="H534" t="n">
-        <v>3.546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="535">
@@ -15415,7 +15415,7 @@
         <v>0</v>
       </c>
       <c r="H535" t="n">
-        <v>2.5964</v>
+        <v>0</v>
       </c>
     </row>
     <row r="536">
@@ -15443,7 +15443,7 @@
         <v>0</v>
       </c>
       <c r="H536" t="n">
-        <v>2.9127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537">
@@ -15471,7 +15471,7 @@
         <v>0</v>
       </c>
       <c r="H537" t="n">
-        <v>2.7285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -15499,7 +15499,7 @@
         <v>0</v>
       </c>
       <c r="H538" t="n">
-        <v>2.308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="539">
@@ -15527,7 +15527,7 @@
         <v>0</v>
       </c>
       <c r="H539" t="n">
-        <v>4.5536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540">
@@ -15580,7 +15580,7 @@
         <v>0</v>
       </c>
       <c r="G541" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -15608,7 +15608,7 @@
         <v>0</v>
       </c>
       <c r="G542" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -15624,7 +15624,7 @@
         <v>0</v>
       </c>
       <c r="C543" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D543" t="n">
         <v>0</v>
@@ -15636,7 +15636,7 @@
         <v>0</v>
       </c>
       <c r="G543" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>0</v>
       </c>
       <c r="C544" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D544" t="n">
         <v>0</v>
@@ -15664,7 +15664,7 @@
         <v>0</v>
       </c>
       <c r="G544" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="D545" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E545" t="n">
         <v>0</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="D546" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E546" t="n">
         <v>0</v>
@@ -15720,7 +15720,7 @@
         <v>0</v>
       </c>
       <c r="G546" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="D547" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E547" t="n">
         <v>0</v>
@@ -15748,7 +15748,7 @@
         <v>0</v>
       </c>
       <c r="G547" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -15764,7 +15764,7 @@
         <v>0</v>
       </c>
       <c r="C548" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D548" t="n">
         <v>0</v>
@@ -15776,7 +15776,7 @@
         <v>0</v>
       </c>
       <c r="G548" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16128,7 +16128,7 @@
         <v>0</v>
       </c>
       <c r="C561" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D561" t="n">
         <v>0</v>
@@ -17615,7 +17615,7 @@
         <v>0</v>
       </c>
       <c r="D614" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E614" t="n">
         <v>0</v>
@@ -18032,7 +18032,7 @@
         <v>0</v>
       </c>
       <c r="C629" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D629" t="n">
         <v>0</v>
@@ -18259,7 +18259,7 @@
         <v>0</v>
       </c>
       <c r="D637" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E637" t="n">
         <v>0</v>
@@ -18595,7 +18595,7 @@
         <v>0</v>
       </c>
       <c r="D649" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E649" t="n">
         <v>0</v>
@@ -19631,7 +19631,7 @@
         <v>0</v>
       </c>
       <c r="D686" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E686" t="n">
         <v>0</v>
@@ -19771,7 +19771,7 @@
         <v>0</v>
       </c>
       <c r="D691" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E691" t="n">
         <v>0</v>
@@ -19967,7 +19967,7 @@
         <v>0</v>
       </c>
       <c r="D698" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E698" t="n">
         <v>0</v>
@@ -20583,7 +20583,7 @@
         <v>0</v>
       </c>
       <c r="D720" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E720" t="n">
         <v>0</v>
@@ -20608,7 +20608,7 @@
         <v>0</v>
       </c>
       <c r="C721" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D721" t="n">
         <v>0</v>
@@ -21199,7 +21199,7 @@
         <v>0</v>
       </c>
       <c r="D742" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E742" t="n">
         <v>0</v>
@@ -22092,7 +22092,7 @@
         <v>0</v>
       </c>
       <c r="C774" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D774" t="n">
         <v>0</v>
@@ -22848,7 +22848,7 @@
         <v>0</v>
       </c>
       <c r="C801" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D801" t="n">
         <v>0</v>
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>47.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -23245,7 +23245,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -23257,10 +23257,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>52.7</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>46.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -23276,7 +23276,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -23285,7 +23285,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>99.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>29.2397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>36.5546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23400,7 +23400,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>45.5445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -23456,7 +23456,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>26.5432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -23484,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>45.2554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>19.1176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>26.8041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>34.6153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>15.8301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>35.9154</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -23708,7 +23708,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>21.2643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>24.8062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -23792,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>21.2643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -23848,7 +23848,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>42.5531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -23876,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>37.8151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>89.041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -23932,7 +23932,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>93.7106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>31.5384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>32.4675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -24016,7 +24016,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>24.3421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>29.4871</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -24100,7 +24100,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>18.4782</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -24184,7 +24184,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -24212,7 +24212,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>19.6202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>23.0769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -24324,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>30.3886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -24408,7 +24408,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>34.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -24436,7 +24436,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>62.6436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -24492,7 +24492,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>35.1351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -24548,7 +24548,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>45.9459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>27.8688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -24632,7 +24632,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>55.5555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -24716,7 +24716,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>34.3661</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -24772,7 +24772,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>24.8275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -24800,7 +24800,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>33.1081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -24828,7 +24828,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>84.5864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -24856,7 +24856,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>46.1794</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -24884,7 +24884,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>23.9263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -24996,7 +24996,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>54.0983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -25180,7 +25180,7 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>19.7301</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -25332,7 +25332,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>55.1928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -25360,7 +25360,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>42.2077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -25416,7 +25416,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>26.6932</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -25612,7 +25612,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>46.0843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -25668,7 +25668,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>83.91160000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -25696,7 +25696,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>47.1365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -25724,7 +25724,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>36.4269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -25752,7 +25752,7 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>32.8828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -25780,7 +25780,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>33.7552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -25808,7 +25808,7 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>34.2569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -26088,7 +26088,7 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>43.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -26116,7 +26116,7 @@
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>56.4393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -26144,7 +26144,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>38.6524</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -26284,7 +26284,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>99.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -26368,7 +26368,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>35.8333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -26396,7 +26396,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>53.9651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -26452,7 +26452,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>29.8136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -26480,7 +26480,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -26508,7 +26508,7 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>43.0952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -26564,7 +26564,7 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>38.2716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -26592,7 +26592,7 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>42.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -26620,7 +26620,7 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>23.841</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -26648,7 +26648,7 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>21.6783</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -26704,7 +26704,7 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>27.4193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -26732,7 +26732,7 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>65.9898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -26760,7 +26760,7 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>57.9999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -26788,7 +26788,7 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>52.6315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -26816,7 +26816,7 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>57.1428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -26872,7 +26872,7 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>48.6486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -27000,7 +27000,7 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -27012,7 +27012,7 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>71.021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -27096,7 +27096,7 @@
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>30.5825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -27180,7 +27180,7 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>35.4243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -27208,7 +27208,7 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -27320,7 +27320,7 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -27348,7 +27348,7 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>40.2684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -27445,7 +27445,7 @@
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -27457,7 +27457,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>50.6736</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -27501,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -27513,7 +27513,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>59.7733</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -27532,7 +27532,7 @@
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -27541,7 +27541,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>74.69710000000001</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>45.6431</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -27613,7 +27613,7 @@
         <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -27625,7 +27625,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>55.5996</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -27684,7 +27684,7 @@
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>57.6687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -28076,7 +28076,7 @@
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>38.5542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -28104,7 +28104,7 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>41.3793</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -28132,7 +28132,7 @@
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>51.1494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -28160,7 +28160,7 @@
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>43.7956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -28188,7 +28188,7 @@
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>28.8288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -28213,7 +28213,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -28288,7 +28288,7 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
@@ -28297,7 +28297,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>54.1501</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>17.1527</v>
+        <v>99.5</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
@@ -28381,7 +28381,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>82.3472</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -28409,7 +28409,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>92.2924</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -28465,7 +28465,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>79.8283</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -28552,7 +28552,7 @@
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>70.5882</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -28568,7 +28568,7 @@
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
@@ -28577,7 +28577,7 @@
         <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>73.55929999999999</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -28649,7 +28649,7 @@
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
+        <v>66.11239999999999</v>
       </c>
       <c r="D200" t="n">
         <v>0</v>
@@ -28658,10 +28658,10 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>33.3875</v>
       </c>
       <c r="G200" t="n">
-        <v>33.3875</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -28677,7 +28677,7 @@
         <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -28689,7 +28689,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>38.1331</v>
+        <v>0</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -28708,7 +28708,7 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -28717,10 +28717,10 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>53.6935</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>45.8064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -28748,7 +28748,7 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>28.6585</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -28776,7 +28776,7 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>81.6793</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -28832,7 +28832,7 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>52.4027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -28944,7 +28944,7 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>15.4929</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -29000,7 +29000,7 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>72.41370000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -29028,7 +29028,7 @@
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>42.233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -29056,7 +29056,7 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>40.099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -29084,7 +29084,7 @@
         <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>50.4504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -29112,7 +29112,7 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>20.6896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -29128,7 +29128,7 @@
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>60.055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -29168,7 +29168,7 @@
         <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>56.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -29193,10 +29193,10 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>64.66849999999999</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>34.8314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -29224,7 +29224,7 @@
         <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>33.5403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -29392,7 +29392,7 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>20.8053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -29560,7 +29560,7 @@
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>17.6678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -29588,7 +29588,7 @@
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>25.1908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -29840,7 +29840,7 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>26.7857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -29993,7 +29993,7 @@
         <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -30005,10 +30005,10 @@
         <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>56.4713</v>
+        <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>43.0286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -30021,7 +30021,7 @@
         <v>0</v>
       </c>
       <c r="C249" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D249" t="n">
         <v>0</v>
@@ -30033,10 +30033,10 @@
         <v>0</v>
       </c>
       <c r="G249" t="n">
-        <v>75.15479999999999</v>
+        <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>24.3451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -30232,7 +30232,7 @@
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>42.4657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -30260,7 +30260,7 @@
         <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>53.2544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -30273,7 +30273,7 @@
         <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D258" t="n">
         <v>0</v>
@@ -30285,10 +30285,10 @@
         <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>57.9932</v>
+        <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>41.5067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -30301,7 +30301,7 @@
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -30313,10 +30313,10 @@
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>65.4512</v>
+        <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>34.0487</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -30512,7 +30512,7 @@
         <v>0</v>
       </c>
       <c r="H266" t="n">
-        <v>25.1798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -30540,7 +30540,7 @@
         <v>0</v>
       </c>
       <c r="H267" t="n">
-        <v>22.6027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -30568,7 +30568,7 @@
         <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>46.3659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -30596,7 +30596,7 @@
         <v>0</v>
       </c>
       <c r="H269" t="n">
-        <v>55.4644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -30652,7 +30652,7 @@
         <v>0</v>
       </c>
       <c r="H271" t="n">
-        <v>34.5132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -30708,7 +30708,7 @@
         <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>21.8085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -30736,7 +30736,7 @@
         <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>27.6785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -30820,7 +30820,7 @@
         <v>0</v>
       </c>
       <c r="H277" t="n">
-        <v>32.971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -30889,7 +30889,7 @@
         <v>0</v>
       </c>
       <c r="C280" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D280" t="n">
         <v>0</v>
@@ -30901,7 +30901,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>73.1514</v>
+        <v>0</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -30917,7 +30917,7 @@
         <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>0</v>
+        <v>81.2204</v>
       </c>
       <c r="D281" t="n">
         <v>0</v>
@@ -30926,7 +30926,7 @@
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>18.2795</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -30945,7 +30945,7 @@
         <v>0</v>
       </c>
       <c r="C282" t="n">
-        <v>0</v>
+        <v>60.8673</v>
       </c>
       <c r="D282" t="n">
         <v>0</v>
@@ -30957,7 +30957,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>60.8673</v>
+        <v>0</v>
       </c>
       <c r="H282" t="n">
         <v>38.6326</v>
@@ -31016,7 +31016,7 @@
         <v>0</v>
       </c>
       <c r="H284" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -31100,7 +31100,7 @@
         <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>27.6785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -31184,7 +31184,7 @@
         <v>0</v>
       </c>
       <c r="H290" t="n">
-        <v>60.2941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -31212,7 +31212,7 @@
         <v>0</v>
       </c>
       <c r="H291" t="n">
-        <v>46.2264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -31240,7 +31240,7 @@
         <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>40.196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -31256,7 +31256,7 @@
         <v>0</v>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E293" t="n">
         <v>0</v>
@@ -31296,7 +31296,7 @@
         <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>55.4545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -31309,7 +31309,7 @@
         <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D295" t="n">
         <v>0</v>
@@ -31318,7 +31318,7 @@
         <v>0</v>
       </c>
       <c r="F295" t="n">
-        <v>54.6771</v>
+        <v>0</v>
       </c>
       <c r="G295" t="n">
         <v>0</v>
@@ -31408,7 +31408,7 @@
         <v>0</v>
       </c>
       <c r="H298" t="n">
-        <v>38.6831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -31421,7 +31421,7 @@
         <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D299" t="n">
         <v>0</v>
@@ -31433,7 +31433,7 @@
         <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>85.5973</v>
+        <v>0</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -31449,7 +31449,7 @@
         <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D300" t="n">
         <v>0</v>
@@ -31461,7 +31461,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>28.0228</v>
+        <v>0</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -31477,7 +31477,7 @@
         <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D301" t="n">
         <v>0</v>
@@ -31520,7 +31520,7 @@
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>80.8695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -31548,7 +31548,7 @@
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>91.1764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -31576,7 +31576,7 @@
         <v>0</v>
       </c>
       <c r="H304" t="n">
-        <v>94.6808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -31629,7 +31629,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>89.89360000000001</v>
+        <v>0</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -31673,7 +31673,7 @@
         <v>0</v>
       </c>
       <c r="C308" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D308" t="n">
         <v>0</v>
@@ -31716,7 +31716,7 @@
         <v>0</v>
       </c>
       <c r="H309" t="n">
-        <v>41.4322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -31732,7 +31732,7 @@
         <v>0</v>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E310" t="n">
         <v>0</v>
@@ -31741,7 +31741,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>99.5</v>
+        <v>0</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -31772,7 +31772,7 @@
         <v>0</v>
       </c>
       <c r="H311" t="n">
-        <v>50.4249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -31828,7 +31828,7 @@
         <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>31.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -31884,7 +31884,7 @@
         <v>0</v>
       </c>
       <c r="H315" t="n">
-        <v>63.327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -31912,7 +31912,7 @@
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>30.4347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -31940,7 +31940,7 @@
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>41.7475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -31996,7 +31996,7 @@
         <v>0</v>
       </c>
       <c r="H319" t="n">
-        <v>34.8148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -32024,7 +32024,7 @@
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>39.4736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -32037,7 +32037,7 @@
         <v>0</v>
       </c>
       <c r="C321" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D321" t="n">
         <v>0</v>
@@ -32049,10 +32049,10 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>62.1301</v>
+        <v>0</v>
       </c>
       <c r="H321" t="n">
-        <v>37.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -32080,7 +32080,7 @@
         <v>0</v>
       </c>
       <c r="H322" t="n">
-        <v>23.3766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="H323" t="n">
-        <v>30.6666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -32164,7 +32164,7 @@
         <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>28.0991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -32248,7 +32248,7 @@
         <v>0</v>
       </c>
       <c r="H328" t="n">
-        <v>18.0851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -32276,7 +32276,7 @@
         <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>44.382</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -32304,7 +32304,7 @@
         <v>0</v>
       </c>
       <c r="H330" t="n">
-        <v>42.2764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -32332,7 +32332,7 @@
         <v>0</v>
       </c>
       <c r="H331" t="n">
-        <v>35.8333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -32444,7 +32444,7 @@
         <v>0</v>
       </c>
       <c r="H335" t="n">
-        <v>28.0701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -32556,7 +32556,7 @@
         <v>0</v>
       </c>
       <c r="H339" t="n">
-        <v>27.1186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -32584,7 +32584,7 @@
         <v>0</v>
       </c>
       <c r="H340" t="n">
-        <v>38.0952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -32612,7 +32612,7 @@
         <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>63.0952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -32724,7 +32724,7 @@
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>40.8602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -32752,7 +32752,7 @@
         <v>0</v>
       </c>
       <c r="H346" t="n">
-        <v>32.9479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -32808,7 +32808,7 @@
         <v>0</v>
       </c>
       <c r="H348" t="n">
-        <v>38.1679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -32892,7 +32892,7 @@
         <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>27.8688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
@@ -32948,7 +32948,7 @@
         <v>0</v>
       </c>
       <c r="H353" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -32976,7 +32976,7 @@
         <v>0</v>
       </c>
       <c r="H354" t="n">
-        <v>42.2018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -33032,7 +33032,7 @@
         <v>0</v>
       </c>
       <c r="H356" t="n">
-        <v>49.2424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -33116,7 +33116,7 @@
         <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>50.4761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -33129,7 +33129,7 @@
         <v>0</v>
       </c>
       <c r="C360" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D360" t="n">
         <v>0</v>
@@ -33141,10 +33141,10 @@
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>56.7708</v>
+        <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>42.7291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -33188,7 +33188,7 @@
         <v>0</v>
       </c>
       <c r="D362" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E362" t="n">
         <v>0</v>
@@ -33228,7 +33228,7 @@
         <v>0</v>
       </c>
       <c r="H363" t="n">
-        <v>40.3508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -33244,7 +33244,7 @@
         <v>0</v>
       </c>
       <c r="D364" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E364" t="n">
         <v>0</v>
@@ -33253,10 +33253,10 @@
         <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>54.0454</v>
+        <v>0</v>
       </c>
       <c r="H364" t="n">
-        <v>45.4545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -33284,7 +33284,7 @@
         <v>0</v>
       </c>
       <c r="H365" t="n">
-        <v>64.7058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -33312,7 +33312,7 @@
         <v>0</v>
       </c>
       <c r="H366" t="n">
-        <v>25.5474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -33340,7 +33340,7 @@
         <v>0</v>
       </c>
       <c r="H367" t="n">
-        <v>42.9718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -33396,7 +33396,7 @@
         <v>0</v>
       </c>
       <c r="H369" t="n">
-        <v>38.0952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -33412,7 +33412,7 @@
         <v>0</v>
       </c>
       <c r="D370" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E370" t="n">
         <v>0</v>
@@ -33424,7 +33424,7 @@
         <v>0</v>
       </c>
       <c r="H370" t="n">
-        <v>52.8239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -33480,7 +33480,7 @@
         <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>80.62820000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -33508,7 +33508,7 @@
         <v>0</v>
       </c>
       <c r="H373" t="n">
-        <v>41.3888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -33676,7 +33676,7 @@
         <v>0</v>
       </c>
       <c r="H379" t="n">
-        <v>31.6129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -33704,7 +33704,7 @@
         <v>0</v>
       </c>
       <c r="H380" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -33717,7 +33717,7 @@
         <v>0</v>
       </c>
       <c r="C381" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D381" t="n">
         <v>0</v>
@@ -33729,10 +33729,10 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>50.2667</v>
+        <v>0</v>
       </c>
       <c r="H381" t="n">
-        <v>49.2332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -33745,7 +33745,7 @@
         <v>0</v>
       </c>
       <c r="C382" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D382" t="n">
         <v>0</v>
@@ -33757,10 +33757,10 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>60.8647</v>
+        <v>0</v>
       </c>
       <c r="H382" t="n">
-        <v>38.6352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -33816,7 +33816,7 @@
         <v>0</v>
       </c>
       <c r="H384" t="n">
-        <v>44.2922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -33872,7 +33872,7 @@
         <v>0</v>
       </c>
       <c r="H386" t="n">
-        <v>53.6437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -33900,7 +33900,7 @@
         <v>0</v>
       </c>
       <c r="H387" t="n">
-        <v>45.5696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -33928,7 +33928,7 @@
         <v>0</v>
       </c>
       <c r="H388" t="n">
-        <v>41.7721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -33956,7 +33956,7 @@
         <v>0</v>
       </c>
       <c r="H389" t="n">
-        <v>50.6329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -33984,7 +33984,7 @@
         <v>0</v>
       </c>
       <c r="H390" t="n">
-        <v>46.8354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -34012,7 +34012,7 @@
         <v>0</v>
       </c>
       <c r="H391" t="n">
-        <v>48.1927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -34040,7 +34040,7 @@
         <v>0</v>
       </c>
       <c r="H392" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393">
@@ -34096,7 +34096,7 @@
         <v>0</v>
       </c>
       <c r="H394" t="n">
-        <v>37.2093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -34152,7 +34152,7 @@
         <v>0</v>
       </c>
       <c r="H396" t="n">
-        <v>25.2032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -34180,7 +34180,7 @@
         <v>0</v>
       </c>
       <c r="H397" t="n">
-        <v>43.5897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -34208,7 +34208,7 @@
         <v>0</v>
       </c>
       <c r="H398" t="n">
-        <v>36.9047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399">
@@ -34236,7 +34236,7 @@
         <v>0</v>
       </c>
       <c r="H399" t="n">
-        <v>53.4246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -34264,7 +34264,7 @@
         <v>0</v>
       </c>
       <c r="H400" t="n">
-        <v>46.9696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -34280,7 +34280,7 @@
         <v>0</v>
       </c>
       <c r="D401" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E401" t="n">
         <v>0</v>
@@ -34289,10 +34289,10 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>60.9285</v>
+        <v>0</v>
       </c>
       <c r="H401" t="n">
-        <v>38.5714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -34320,7 +34320,7 @@
         <v>0</v>
       </c>
       <c r="H402" t="n">
-        <v>98.1818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -34404,7 +34404,7 @@
         <v>0</v>
       </c>
       <c r="H405" t="n">
-        <v>97.2972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -34432,7 +34432,7 @@
         <v>0</v>
       </c>
       <c r="H406" t="n">
-        <v>30.9417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -34448,7 +34448,7 @@
         <v>0</v>
       </c>
       <c r="D407" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E407" t="n">
         <v>0</v>
@@ -34457,10 +34457,10 @@
         <v>0</v>
       </c>
       <c r="G407" t="n">
-        <v>41.768</v>
+        <v>0</v>
       </c>
       <c r="H407" t="n">
-        <v>57.7319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -34516,7 +34516,7 @@
         <v>0</v>
       </c>
       <c r="H409" t="n">
-        <v>80.95229999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410">
@@ -34569,10 +34569,10 @@
         <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>69.98050000000001</v>
+        <v>0</v>
       </c>
       <c r="H411" t="n">
-        <v>29.5194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -34600,7 +34600,7 @@
         <v>0</v>
       </c>
       <c r="H412" t="n">
-        <v>35.119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413">
@@ -34628,7 +34628,7 @@
         <v>0</v>
       </c>
       <c r="H413" t="n">
-        <v>60.6299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -34712,7 +34712,7 @@
         <v>0</v>
       </c>
       <c r="H416" t="n">
-        <v>44.1379</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -34992,7 +34992,7 @@
         <v>0</v>
       </c>
       <c r="H426" t="n">
-        <v>98.60129999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427">
@@ -35020,7 +35020,7 @@
         <v>0</v>
       </c>
       <c r="H427" t="n">
-        <v>44.8484</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -35064,7 +35064,7 @@
         <v>0</v>
       </c>
       <c r="D429" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E429" t="n">
         <v>0</v>
@@ -35216,7 +35216,7 @@
         <v>0</v>
       </c>
       <c r="H434" t="n">
-        <v>25.4098</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435">
@@ -35244,7 +35244,7 @@
         <v>0</v>
       </c>
       <c r="H435" t="n">
-        <v>55.7377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436">
@@ -35272,7 +35272,7 @@
         <v>0</v>
       </c>
       <c r="H436" t="n">
-        <v>57.5757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -35300,7 +35300,7 @@
         <v>0</v>
       </c>
       <c r="H437" t="n">
-        <v>60.8695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -35328,7 +35328,7 @@
         <v>0</v>
       </c>
       <c r="H438" t="n">
-        <v>42.2018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439">
@@ -35356,7 +35356,7 @@
         <v>0</v>
       </c>
       <c r="H439" t="n">
-        <v>43.6507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
@@ -35384,7 +35384,7 @@
         <v>0</v>
       </c>
       <c r="H440" t="n">
-        <v>60.1398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -35428,7 +35428,7 @@
         <v>0</v>
       </c>
       <c r="D442" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E442" t="n">
         <v>0</v>
@@ -35468,7 +35468,7 @@
         <v>0</v>
       </c>
       <c r="H443" t="n">
-        <v>44.6808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444">
@@ -35524,7 +35524,7 @@
         <v>0</v>
       </c>
       <c r="H445" t="n">
-        <v>58.6538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446">
@@ -35608,7 +35608,7 @@
         <v>0</v>
       </c>
       <c r="H448" t="n">
-        <v>33.913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="449">
@@ -35692,7 +35692,7 @@
         <v>0</v>
       </c>
       <c r="H451" t="n">
-        <v>30.2158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -35720,7 +35720,7 @@
         <v>0</v>
       </c>
       <c r="H452" t="n">
-        <v>45.8536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -35776,7 +35776,7 @@
         <v>0</v>
       </c>
       <c r="H454" t="n">
-        <v>54.3478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -35804,7 +35804,7 @@
         <v>0</v>
       </c>
       <c r="H455" t="n">
-        <v>44.086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456">
@@ -35916,7 +35916,7 @@
         <v>0</v>
       </c>
       <c r="H459" t="n">
-        <v>36.8932</v>
+        <v>0</v>
       </c>
     </row>
     <row r="460">
@@ -36000,7 +36000,7 @@
         <v>0</v>
       </c>
       <c r="H462" t="n">
-        <v>26.198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463">
@@ -36044,7 +36044,7 @@
         <v>0</v>
       </c>
       <c r="D464" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E464" t="n">
         <v>0</v>
@@ -36053,10 +36053,10 @@
         <v>0</v>
       </c>
       <c r="G464" t="n">
-        <v>46.6641</v>
+        <v>0</v>
       </c>
       <c r="H464" t="n">
-        <v>52.8358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="465">
@@ -36140,7 +36140,7 @@
         <v>0</v>
       </c>
       <c r="H467" t="n">
-        <v>28.9617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="468">
@@ -36196,7 +36196,7 @@
         <v>0</v>
       </c>
       <c r="H469" t="n">
-        <v>94.2028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="470">
@@ -36224,7 +36224,7 @@
         <v>0</v>
       </c>
       <c r="H470" t="n">
-        <v>28.1609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -36252,7 +36252,7 @@
         <v>0</v>
       </c>
       <c r="H471" t="n">
-        <v>45.5357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472">
@@ -36280,7 +36280,7 @@
         <v>0</v>
       </c>
       <c r="H472" t="n">
-        <v>60.4878</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473">
@@ -36308,7 +36308,7 @@
         <v>0</v>
       </c>
       <c r="H473" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474">
@@ -36324,7 +36324,7 @@
         <v>0</v>
       </c>
       <c r="D474" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E474" t="n">
         <v>0</v>
@@ -36336,7 +36336,7 @@
         <v>0</v>
       </c>
       <c r="H474" t="n">
-        <v>77.9661</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475">
@@ -36352,7 +36352,7 @@
         <v>0</v>
       </c>
       <c r="D475" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E475" t="n">
         <v>0</v>
@@ -36361,7 +36361,7 @@
         <v>0</v>
       </c>
       <c r="G475" t="n">
-        <v>51.9813</v>
+        <v>0</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -36476,7 +36476,7 @@
         <v>0</v>
       </c>
       <c r="H479" t="n">
-        <v>38.5454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -36700,7 +36700,7 @@
         <v>0</v>
       </c>
       <c r="H487" t="n">
-        <v>23.5714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488">
@@ -36756,7 +36756,7 @@
         <v>0</v>
       </c>
       <c r="H489" t="n">
-        <v>22.4489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="490">
@@ -36784,7 +36784,7 @@
         <v>0</v>
       </c>
       <c r="H490" t="n">
-        <v>42.0689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="491">
@@ -36812,7 +36812,7 @@
         <v>0</v>
       </c>
       <c r="H491" t="n">
-        <v>62.3529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="492">
@@ -36840,7 +36840,7 @@
         <v>0</v>
       </c>
       <c r="H492" t="n">
-        <v>38.3458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493">
@@ -36868,7 +36868,7 @@
         <v>0</v>
       </c>
       <c r="H493" t="n">
-        <v>62.0512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494">
@@ -36896,7 +36896,7 @@
         <v>0</v>
       </c>
       <c r="H494" t="n">
-        <v>43.8016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="495">
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="H496" t="n">
-        <v>48.8549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497">
@@ -36980,7 +36980,7 @@
         <v>0</v>
       </c>
       <c r="H497" t="n">
-        <v>24.4444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498">
@@ -37036,7 +37036,7 @@
         <v>0</v>
       </c>
       <c r="H499" t="n">
-        <v>37.9032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -37120,7 +37120,7 @@
         <v>0</v>
       </c>
       <c r="H502" t="n">
-        <v>37.8048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="503">
@@ -37484,7 +37484,7 @@
         <v>0</v>
       </c>
       <c r="H515" t="n">
-        <v>44.6153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516">
@@ -37680,7 +37680,7 @@
         <v>0</v>
       </c>
       <c r="H522" t="n">
-        <v>29.0322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523">
@@ -37708,7 +37708,7 @@
         <v>0</v>
       </c>
       <c r="H523" t="n">
-        <v>26.344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
@@ -37736,7 +37736,7 @@
         <v>0</v>
       </c>
       <c r="H524" t="n">
-        <v>22.513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="525">
@@ -37764,7 +37764,7 @@
         <v>0</v>
       </c>
       <c r="H525" t="n">
-        <v>30.8571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="526">
@@ -37792,7 +37792,7 @@
         <v>0</v>
       </c>
       <c r="H526" t="n">
-        <v>41.6666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="527">
@@ -37820,7 +37820,7 @@
         <v>0</v>
       </c>
       <c r="H527" t="n">
-        <v>52.3333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="528">
@@ -37848,7 +37848,7 @@
         <v>0</v>
       </c>
       <c r="H528" t="n">
-        <v>35.1851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="529">
@@ -37876,7 +37876,7 @@
         <v>0</v>
       </c>
       <c r="H529" t="n">
-        <v>37.5939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530">
@@ -37904,7 +37904,7 @@
         <v>0</v>
       </c>
       <c r="H530" t="n">
-        <v>35.5329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -37932,7 +37932,7 @@
         <v>0</v>
       </c>
       <c r="H531" t="n">
-        <v>19.6969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532">
@@ -37960,7 +37960,7 @@
         <v>0</v>
       </c>
       <c r="H532" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533">
@@ -37988,7 +37988,7 @@
         <v>0</v>
       </c>
       <c r="H533" t="n">
-        <v>46.7661</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534">
@@ -38016,7 +38016,7 @@
         <v>0</v>
       </c>
       <c r="H534" t="n">
-        <v>38.4615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="535">
@@ -38044,7 +38044,7 @@
         <v>0</v>
       </c>
       <c r="H535" t="n">
-        <v>28.5714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="536">
@@ -38072,7 +38072,7 @@
         <v>0</v>
       </c>
       <c r="H536" t="n">
-        <v>99.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537">
@@ -38100,7 +38100,7 @@
         <v>0</v>
       </c>
       <c r="H537" t="n">
-        <v>30.8724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -38128,7 +38128,7 @@
         <v>0</v>
       </c>
       <c r="H538" t="n">
-        <v>24.2236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="539">
@@ -38156,7 +38156,7 @@
         <v>0</v>
       </c>
       <c r="H539" t="n">
-        <v>36.1502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540">
@@ -38209,7 +38209,7 @@
         <v>0</v>
       </c>
       <c r="G541" t="n">
-        <v>72.68810000000001</v>
+        <v>0</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -38237,7 +38237,7 @@
         <v>0</v>
       </c>
       <c r="G542" t="n">
-        <v>93.8073</v>
+        <v>0</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -38253,7 +38253,7 @@
         <v>0</v>
       </c>
       <c r="C543" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D543" t="n">
         <v>0</v>
@@ -38265,7 +38265,7 @@
         <v>0</v>
       </c>
       <c r="G543" t="n">
-        <v>40.2961</v>
+        <v>0</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -38281,7 +38281,7 @@
         <v>0</v>
       </c>
       <c r="C544" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D544" t="n">
         <v>0</v>
@@ -38293,7 +38293,7 @@
         <v>0</v>
       </c>
       <c r="G544" t="n">
-        <v>64.5955</v>
+        <v>0</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -38312,7 +38312,7 @@
         <v>0</v>
       </c>
       <c r="D545" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E545" t="n">
         <v>0</v>
@@ -38340,7 +38340,7 @@
         <v>0</v>
       </c>
       <c r="D546" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E546" t="n">
         <v>0</v>
@@ -38349,7 +38349,7 @@
         <v>0</v>
       </c>
       <c r="G546" t="n">
-        <v>71.18429999999999</v>
+        <v>0</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -38368,7 +38368,7 @@
         <v>0</v>
       </c>
       <c r="D547" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E547" t="n">
         <v>0</v>
@@ -38377,7 +38377,7 @@
         <v>0</v>
       </c>
       <c r="G547" t="n">
-        <v>88.7426</v>
+        <v>0</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -38393,7 +38393,7 @@
         <v>0</v>
       </c>
       <c r="C548" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D548" t="n">
         <v>0</v>
@@ -38405,7 +38405,7 @@
         <v>0</v>
       </c>
       <c r="G548" t="n">
-        <v>37.0745</v>
+        <v>0</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -38757,7 +38757,7 @@
         <v>0</v>
       </c>
       <c r="C561" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D561" t="n">
         <v>0</v>
@@ -40244,7 +40244,7 @@
         <v>0</v>
       </c>
       <c r="D614" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E614" t="n">
         <v>0</v>
@@ -40661,7 +40661,7 @@
         <v>0</v>
       </c>
       <c r="C629" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D629" t="n">
         <v>0</v>
@@ -40888,7 +40888,7 @@
         <v>0</v>
       </c>
       <c r="D637" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E637" t="n">
         <v>0</v>
@@ -41224,7 +41224,7 @@
         <v>0</v>
       </c>
       <c r="D649" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E649" t="n">
         <v>0</v>
@@ -42260,7 +42260,7 @@
         <v>0</v>
       </c>
       <c r="D686" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E686" t="n">
         <v>0</v>
@@ -42400,7 +42400,7 @@
         <v>0</v>
       </c>
       <c r="D691" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E691" t="n">
         <v>0</v>
@@ -42596,7 +42596,7 @@
         <v>0</v>
       </c>
       <c r="D698" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E698" t="n">
         <v>0</v>
@@ -43212,7 +43212,7 @@
         <v>0</v>
       </c>
       <c r="D720" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E720" t="n">
         <v>0</v>
@@ -43237,7 +43237,7 @@
         <v>0</v>
       </c>
       <c r="C721" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D721" t="n">
         <v>0</v>
@@ -43828,7 +43828,7 @@
         <v>0</v>
       </c>
       <c r="D742" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="E742" t="n">
         <v>0</v>
@@ -44721,7 +44721,7 @@
         <v>0</v>
       </c>
       <c r="C774" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D774" t="n">
         <v>0</v>
@@ -45477,7 +45477,7 @@
         <v>0</v>
       </c>
       <c r="C801" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="D801" t="n">
         <v>0</v>
